--- a/VerveStacks_VNM/vt_vervestacks_VNM_v1.xlsx
+++ b/VerveStacks_VNM/vt_vervestacks_VNM_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5645DEF5-9D06-4D53-BAFB-4171A4B671FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D239725D-CD88-4F10-B71B-8B836C4379E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6DA63296-9BF4-4D4A-B4E0-06687B2FAF43}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2DE0D8F0-A086-4A6D-913C-5E8BD170C666}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3427,7 +3427,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7E9BF1B-9921-4B0C-9748-7703EC983AEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{422E416D-8107-4644-8268-12A546FDA444}">
   <dimension ref="B9:T117"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9493,7 +9493,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970AEE8B-5745-4858-B118-3B7064601799}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CCE6BA3-AA2A-4BEB-84EC-60673324E562}">
   <dimension ref="B9:T162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17779,7 +17779,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4709089-003A-4BB4-A889-3935ECF51BC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6054FF8B-EE86-4BE2-8ED7-8F31A312EC17}">
   <dimension ref="B9:T332"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -28228,7 +28228,7 @@
         <v>33</v>
       </c>
       <c r="L207">
-        <v>0.18682856720731586</v>
+        <v>0.18682856720731583</v>
       </c>
       <c r="N207" t="s">
         <v>299</v>
@@ -28275,7 +28275,7 @@
         <v>33</v>
       </c>
       <c r="L208">
-        <v>0.18682856720731586</v>
+        <v>0.18682856720731583</v>
       </c>
       <c r="N208" t="s">
         <v>299</v>
@@ -28322,7 +28322,7 @@
         <v>33</v>
       </c>
       <c r="L209">
-        <v>0.18682856720731586</v>
+        <v>0.18682856720731583</v>
       </c>
       <c r="N209" t="s">
         <v>299</v>
@@ -30067,7 +30067,7 @@
         <v>262</v>
       </c>
       <c r="P240" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="Q240" t="s">
         <v>301</v>
@@ -30123,7 +30123,7 @@
         <v>262</v>
       </c>
       <c r="P241" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="Q241" t="s">
         <v>301</v>
@@ -30235,7 +30235,7 @@
         <v>267</v>
       </c>
       <c r="P243" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="Q243" t="s">
         <v>301</v>
@@ -30291,7 +30291,7 @@
         <v>267</v>
       </c>
       <c r="P244" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="Q244" t="s">
         <v>301</v>
@@ -30347,7 +30347,7 @@
         <v>269</v>
       </c>
       <c r="P245" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="Q245" t="s">
         <v>301</v>
@@ -30403,7 +30403,7 @@
         <v>269</v>
       </c>
       <c r="P246" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="Q246" t="s">
         <v>301</v>
@@ -30459,7 +30459,7 @@
         <v>271</v>
       </c>
       <c r="P247" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="Q247" t="s">
         <v>301</v>
@@ -30515,7 +30515,7 @@
         <v>271</v>
       </c>
       <c r="P248" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="Q248" t="s">
         <v>301</v>
@@ -33770,7 +33770,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F48FC03-A960-45D5-AE86-C57A42E1C677}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8118786C-30FC-4C39-B072-B53309377C4D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
